--- a/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/02_Öz Değerlendirme ve Aksiyon Yönetimi/EKG-YNT-PLN-06_nsa_mpa_bulgusu_duzeltici_aksiyon_ve_etkinlik_kapatma_p.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/02_Öz Değerlendirme ve Aksiyon Yönetimi/EKG-YNT-PLN-06_nsa_mpa_bulgusu_duzeltici_aksiyon_ve_etkinlik_kapatma_p.xlsx
@@ -738,7 +738,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-PLN-06&amp;C&amp;"Arial,Regular"&amp;11NSA MPA Bulgusu Düzeltici Aksiyon ve Etkinlik Kapatma Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 09.09.2026
+Revizyon nedeni: Bulgu-faaliyet ve kanıtlı kapanış izleme sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>